--- a/sheets/국악이꽃피는나무/검수/산조의 농음.xlsx
+++ b/sheets/국악이꽃피는나무/검수/산조의 농음.xlsx
@@ -1450,20 +1450,20 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="43.01" customHeight="true">
+    <row r="2" ht="40.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="63.87" customHeight="true">
+    <row r="3" ht="59.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="63.87" customHeight="true">
+    <row r="4" ht="59.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="63.87" customHeight="true">
+    <row r="5" ht="59.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -1535,7 +1535,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="24"/>
     </row>
-    <row r="6" ht="63.87" customHeight="true">
+    <row r="6" ht="59.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" ht="63.87" customHeight="true">
+    <row r="7" ht="59.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -1573,7 +1573,7 @@
       <c r="H7" s="21"/>
       <c r="I7" s="23"/>
     </row>
-    <row r="8" ht="63.87" customHeight="true">
+    <row r="8" ht="59.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -1588,7 +1588,7 @@
       <c r="H8" s="21"/>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" ht="63.87" customHeight="true">
+    <row r="9" ht="59.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="I9" s="22"/>
     </row>
-    <row r="10" ht="63.87" customHeight="true">
+    <row r="10" ht="59.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -1628,7 +1628,7 @@
       <c r="H10" s="21"/>
       <c r="I10" s="23"/>
     </row>
-    <row r="11" ht="63.87" customHeight="true">
+    <row r="11" ht="59.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
       <c r="H11" s="21"/>
       <c r="I11" s="24"/>
     </row>
-    <row r="12" ht="63.87" customHeight="true">
+    <row r="12" ht="59.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="I12" s="22"/>
     </row>
-    <row r="13" ht="63.87" customHeight="true">
+    <row r="13" ht="59.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -1687,7 +1687,7 @@
       <c r="H13" s="21"/>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="63.87" customHeight="true">
+    <row r="14" ht="59.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -1720,6 +1720,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>